--- a/output/graficos_regionales_sexo_edad/plot_intra_nacional_i_ingr_mean_a_2024_nacional.xlsx
+++ b/output/graficos_regionales_sexo_edad/plot_intra_nacional_i_ingr_mean_a_2024_nacional.xlsx
@@ -37,7 +37,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-08 09:44</t>
+    <t xml:space="preserve">2026-09-18 09:03</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
